--- a/productos.xlsx
+++ b/productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="67">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -139,19 +139,53 @@
     <t xml:space="preserve">respuesta</t>
   </si>
   <si>
-    <t xml:space="preserve">¿Qué es Triptolemus?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENDIENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cómo se conservan los productos?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cómo se realiza un pedido?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Hay disponibilidad permanente?</t>
+    <t xml:space="preserve">¿Quiénes no deberían consumir hongos con psilocibina?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se recomienda evitar la psilocibina, o no consumirla sin una evaluación médica especializada, en los siguientes casos:
+Personas con antecedentes personales de psicosis, esquizofrenia o trastorno bipolar, especialmente si han presentado manía.
+Personas con enfermedades cardiovasculares graves o hipertensión no controlada.
+Personas que toman litio, debido al posible aumento del riesgo de convulsiones.
+Personas embarazadas o en periodo de lactancia, por la falta de evidencia suficiente sobre su seguridad.
+Personas que toman antidepresivos u otros psicofármacos: las interacciones varían según el medicamento. Es importante consultar con un profesional y no suspender ni modificar la medicación por cuenta propia.
+Esta lista no es exhaustiva. Si tienes alguna enfermedad o tomas medicamentos, consulta antes con un profesional sanitario.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto duran los efectos?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los efectos principales suelen durar entre 4 y 6 horas, aunque pueden variar según la persona, el hongo y la cantidad de psilocibina ingerida. Los efectos suelen comenzar entre 20 y 40 minutos después de consumirlos y alcanzar su mayor intensidad aproximadamente entre los 60 y 90 minutos.  Algunas personas pueden experimentar cansancio, alteraciones del sueño o una sensación de estar diferentes durante más tiempo. Por eso, no conviene planificar actividades importantes para el resto del día ni conducir mientras persistan los efectos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Puedo consumirlos estando solo?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo más prudente es no consumirlos a solas, especialmente si es tu primera experiencia. Se recomienda contar con una persona de confianza, sobria y capaz de acompañarte durante toda la experiencia, sin juzgarte y preparada para pedir ayuda si es necesario.  Si decides hacerlo estando solo, avisa previamente a alguien de confianza, acuerda que se comunique contigo y asegúrate de poder pedir ayuda. Ten presente que estas medidas no eliminan los riesgos de estar sin compañía.  Evita conducir, salir a lugares peligrosos, acercarte a balcones o cuerpos de agua, y mezclar los hongos con alcohol u otras drogas.  No tomes decisiones importantes ni realices cambios importantes en tu vida mientras estés bajo sus efectos. Espera a estar completamente sobrio para evaluar la experiencia con perspectiva.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto duran los hongos deshidratados?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si se mantienen protegidos de la humedad, el calor, la luz y el oxígeno, los hongos pueden conservar gran parte de su potencia durante meses. En mi experiencia, he conservado hongos deshidratados durante más de siete meses en un recipiente hermético dentro de la refrigeradora con una potencia relativamente buena.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Puedo mezclarlos con alcohol u otras sustancias? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo más prudente es evitar las mezclas. Pueden hacer que los efectos sean más impredecibles y dificultar que reconozcas o gestiones una reacción adversa. Las interacciones dependen de las sustancias implicadas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué es una microdosis? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En la literatura sobre microdosificación se encuentran cantidades de aproximadamente 0,1 a 0,5 gramos de hongos deshidratados. Nuestras cápsulas contienen 0,2 gramos de material fúngico deshidratado. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan seguido se toman las microdosis? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existen dos protocolos: el de Fadiman y el de Stamets. El primero fue popularizado por el psicólogo James Fadiman en su libro The Psychedelic Explorer's Guide (2011). Su esquema más conocido alterna un día de consumo con dos días sin consumo. Se difundió como una manera de observar los efectos y dejar intervalos entre tomas, entre otras razones para reducir la preocupación por el desarrollo de tolerancia. Por otro lado, el Protocolo de Stamets combina la microdosificación de psilocibina con melena de león (Hericium erinaceus) y niacina (vitamina B3), con un esquema popular de cuatro días de uso y tres de descanso.</t>
   </si>
   <si>
     <t xml:space="preserve">clave</t>
@@ -207,7 +241,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,9 +279,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -266,12 +301,6 @@
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -325,7 +354,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -344,6 +373,14 @@
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -366,7 +403,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -812,8 +849,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -3860,7 +3897,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
@@ -3868,41 +3905,53 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
@@ -4016,28 +4065,28 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>44</v>
+      <c r="A1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>46</v>
+      <c r="A2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8" t="s">
-        <v>48</v>
+      <c r="A3" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4063,48 +4112,48 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>49</v>
+      <c r="A1" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>50</v>
+      <c r="A2" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
-        <v>51</v>
+      <c r="A3" s="12" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>52</v>
+      <c r="A4" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>53</v>
+      <c r="A5" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>54</v>
+      <c r="A6" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>55</v>
+      <c r="A7" s="12" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>56</v>
+      <c r="A8" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>57</v>
+      <c r="A9" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="74">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -131,6 +131,27 @@
   </si>
   <si>
     <t xml:space="preserve">imagenes\Mxa.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTBVI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panaeolus Cyancescens TTBVI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exótico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muy Fuertes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variedad de Panaeolus Cyanescens hallada en bajo un árbol de tamarindo en las British Virgin Islands. Conocida por ser el hongo más potente del mundo en contenido de psilocibina a la fecha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imagenes\Ttbvi.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">pregunta</t>
@@ -923,19 +944,39 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="M6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3891,66 +3932,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4066,27 +4107,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="10" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4113,47 +4154,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="74">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -375,7 +375,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -397,10 +397,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -977,7 +973,9 @@
       <c r="L6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="3"/>
+      <c r="M6" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
@@ -3978,16 +3976,16 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -4106,27 +4104,27 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4153,47 +4151,47 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>73</v>
       </c>
     </row>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -142,7 +142,7 @@
     <t xml:space="preserve">Exótico</t>
   </si>
   <si>
-    <t xml:space="preserve">Muy Fuertes</t>
+    <t xml:space="preserve">Muy fuertes</t>
   </si>
   <si>
     <t xml:space="preserve">Variedad de Panaeolus Cyanescens hallada en bajo un árbol de tamarindo en las British Virgin Islands. Conocida por ser el hongo más potente del mundo en contenido de psilocibina a la fecha.</t>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" state="visible" r:id="rId3"/>
@@ -200,13 +200,13 @@
     <t xml:space="preserve">¿Qué es una microdosis? </t>
   </si>
   <si>
-    <t xml:space="preserve">En la literatura sobre microdosificación se encuentran cantidades de aproximadamente 0,1 a 0,5 gramos de hongos deshidratados. Nuestras cápsulas contienen 0,2 gramos de material fúngico deshidratado. </t>
+    <t xml:space="preserve">Las microdosis son cantidades pequeñas de una sustancia psicodélica que se consumen con la intención de experimentar efectos sutiles, sin provocar las alteraciones perceptivas intensas asociadas a dosis mayores.  En el caso de los hongos con psilocibina, no existe una definición universal de microdosis. La cantidad de psilocibina puede variar considerablemente entre hongos, incluso dentro de una misma especie, por lo que el peso del material no permite predecir con precisión sus efectos.  Algunas personas recurren a la microdosificación con la intención de mejorar su estado de ánimo, concentración o creatividad. Sin embargo, la evidencia científica disponible todavía no permite afirmar de manera concluyente que produzca estos beneficios de forma consistente.  La práctica se popularizó durante la década de 2010, junto con diferentes protocolos de administración, como los asociados a James Fadiman y Paul Stamets. Estos protocolos son propuestas de uso popularizadas, no tratamientos médicos cuya eficacia y seguridad estén establecidas.</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué tan seguido se toman las microdosis? </t>
   </si>
   <si>
-    <t xml:space="preserve">Existen dos protocolos: el de Fadiman y el de Stamets. El primero fue popularizado por el psicólogo James Fadiman en su libro The Psychedelic Explorer's Guide (2011). Su esquema más conocido alterna un día de consumo con dos días sin consumo. Se difundió como una manera de observar los efectos y dejar intervalos entre tomas, entre otras razones para reducir la preocupación por el desarrollo de tolerancia. Por otro lado, el Protocolo de Stamets combina la microdosificación de psilocibina con melena de león (Hericium erinaceus) y niacina (vitamina B3), con un esquema popular de cuatro días de uso y tres de descanso.</t>
+    <t xml:space="preserve">Existen dos protocolos: el de Fadiman y el de Stamets. El primero fue popularizado por el psicólogo James Fadiman en su libro The Psychedelic Explorer's Guide (2011). Su esquema más conocido alterna un día de consumo con dos días sin consumo. Se difundió como una manera de observar los efectos y dejar intervalos entre tomas, entre otras razones para reducir la preocupación por el desarrollo de tolerancia. Por otro lado, el Protocolo de Stamets combina la microdosificación de psilocibina con melena de león (Hericium erinaceus) y niacina (vitamina B3), con un esquema popular de cuatro días de uso y tres de descanso. </t>
   </si>
   <si>
     <t xml:space="preserve">clave</t>
@@ -3976,7 +3976,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>55</v>
       </c>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" state="visible" r:id="rId3"/>
@@ -76,7 +76,7 @@
     <t xml:space="preserve">Suaves</t>
   </si>
   <si>
-    <t xml:space="preserve">Parque Nacional Manu</t>
+    <t xml:space="preserve">Proveniente del Parque Nacional del Manu. Esta cepa presenta las características de un Psilocybe Cubensis salvaje, es decir, adaptado a sobrevivir en la naturaleza: su tallo es largo y delgado y el sombrero se abre por completo liberando millones de esporas. Su potencia no es tan alta comparada con las cepas que han pasado por un proceso de breeding más intensivo.</t>
   </si>
   <si>
     <t xml:space="preserve">Frasco de vidrio</t>
@@ -100,7 +100,7 @@
     <t xml:space="preserve">Fuertes</t>
   </si>
   <si>
-    <t xml:space="preserve">Cruce de Penis envy Hawk y True albino teacher Black cap</t>
+    <t xml:space="preserve">Esta cepa es un cruce de Penis envy Hawk (Hawkeye PE)  y True albino teacher Black cap (TAT Black cap/TBC), dos cepas que ya han pasado por un proceso de breeding y produce unos hongos relativamente fuertes. </t>
   </si>
   <si>
     <t xml:space="preserve">imagenes\Bh.jpg</t>
@@ -112,7 +112,7 @@
     <t xml:space="preserve">Albino Blackhawk</t>
   </si>
   <si>
-    <t xml:space="preserve">Variedad albina del cruce de Penis envy Hawk y True albino teacher Black cap</t>
+    <t xml:space="preserve">Variedad albina del cruce de Penis envy Hawk (Hawkeye PE)  y True albino teacher Black cap (TAT Black cap/TBC), dos cepas que ya han pasado por un proceso de breeding y produce hongos relativamente fuertes. </t>
   </si>
   <si>
     <t xml:space="preserve">imagenes\Abh.jpg</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">Melmac Revert x Albino Penis Envy</t>
   </si>
   <si>
-    <t xml:space="preserve">Melmac Penis envy es una cepa clásica popularizada por la empresa de kits de cultivo Homestead, una de las primeras cepas de los Penis envy. Mientras que el Albino penis envy surgió unos años después al cruzar la cepa Penis envy con Albino A+.</t>
+    <t xml:space="preserve">Esta cepa es del cruce de: Melmac Penis Envy (MPE) y Albino Penis Envy (APE).  Produce hongos relativamente fuertes con patrones de crecimiento similares a los Blackhawk.</t>
   </si>
   <si>
     <t xml:space="preserve">2.5g</t>
@@ -396,12 +396,12 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -792,7 +792,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -829,7 +829,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -845,7 +845,7 @@
       <c r="E3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="4" t="n">
@@ -866,7 +866,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -3969,23 +3969,23 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>57</v>
       </c>
       <c r="B8" s="3" t="s">

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -849,7 +849,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>18</v>
@@ -886,7 +886,7 @@
         <v>29</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>18</v>
@@ -903,7 +903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -923,7 +923,7 @@
         <v>33</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>18</v>
